--- a/nr-update-patient/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/nr-update-patient/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04T08:27:16+00:00</t>
+    <t>2025-10-21T13:57:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4088,7 +4088,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>132</v>
       </c>
@@ -5976,7 +5976,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>222</v>
       </c>
@@ -11193,7 +11193,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
         <v>321</v>
       </c>
@@ -15074,7 +15074,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="89" hidden="true">
+    <row r="89">
       <c r="A89" t="s" s="2">
         <v>368</v>
       </c>
@@ -18959,7 +18959,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="118" hidden="true">
+    <row r="118">
       <c r="A118" t="s" s="2">
         <v>413</v>
       </c>
@@ -19366,7 +19366,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="121" hidden="true">
+    <row r="121">
       <c r="A121" t="s" s="2">
         <v>434</v>
       </c>
@@ -20585,7 +20585,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="130" hidden="true">
+    <row r="130">
       <c r="A130" t="s" s="2">
         <v>503</v>
       </c>
@@ -23023,7 +23023,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="148" hidden="true">
+    <row r="148">
       <c r="A148" t="s" s="2">
         <v>532</v>
       </c>
@@ -23162,7 +23162,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="149" hidden="true">
+    <row r="149">
       <c r="A149" t="s" s="2">
         <v>540</v>
       </c>
@@ -23974,7 +23974,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="155" hidden="true">
+    <row r="155">
       <c r="A155" t="s" s="2">
         <v>574</v>
       </c>
@@ -24109,7 +24109,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="156" hidden="true">
+    <row r="156">
       <c r="A156" t="s" s="2">
         <v>584</v>
       </c>
@@ -24377,7 +24377,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="158" hidden="true">
+    <row r="158">
       <c r="A158" t="s" s="2">
         <v>603</v>
       </c>
@@ -25997,7 +25997,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="170" hidden="true">
+    <row r="170">
       <c r="A170" t="s" s="2">
         <v>681</v>
       </c>
@@ -28010,7 +28010,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="185" hidden="true">
+    <row r="185">
       <c r="A185" t="s" s="2">
         <v>759</v>
       </c>
@@ -31490,7 +31490,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="211" hidden="true">
+    <row r="211">
       <c r="A211" t="s" s="2">
         <v>818</v>
       </c>
@@ -31627,7 +31627,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="212" hidden="true">
+    <row r="212">
       <c r="A212" t="s" s="2">
         <v>821</v>
       </c>
@@ -33920,7 +33920,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="229" hidden="true">
+    <row r="229">
       <c r="A229" t="s" s="2">
         <v>861</v>
       </c>
@@ -34057,7 +34057,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="230" hidden="true">
+    <row r="230">
       <c r="A230" t="s" s="2">
         <v>866</v>
       </c>
@@ -34331,7 +34331,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="232" hidden="true">
+    <row r="232">
       <c r="A232" t="s" s="2">
         <v>870</v>
       </c>
@@ -36350,7 +36350,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="247" hidden="true">
+    <row r="247">
       <c r="A247" t="s" s="2">
         <v>892</v>
       </c>
@@ -36487,7 +36487,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="248" hidden="true">
+    <row r="248">
       <c r="A248" t="s" s="2">
         <v>897</v>
       </c>
@@ -39185,7 +39185,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="268" hidden="true">
+    <row r="268">
       <c r="A268" t="s" s="2">
         <v>926</v>
       </c>
@@ -39322,12 +39322,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AU268">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/nr-update-patient/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/nr-update-patient/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T13:57:20+00:00</t>
+    <t>2025-10-21T14:02:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-patient/ig/StructureDefinition-fr-practitioner-document.xlsx
+++ b/nr-update-patient/ig/StructureDefinition-fr-practitioner-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-21T14:02:08+00:00</t>
+    <t>2025-10-21T14:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
